--- a/tables/datas/common/#Job-职业表.xlsx
+++ b/tables/datas/common/#Job-职业表.xlsx
@@ -568,12 +568,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2,3,4</t>
+          <t>2,3,4,20,21,30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2,3,4</t>
+          <t>2,3,4,20,30</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -600,12 +600,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5,6,7</t>
+          <t>5,6,7,22,23,31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5,6,7</t>
+          <t>5,6,7,22,31</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -632,12 +632,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9,10,11</t>
+          <t>9,10,11,24,25,32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>9,10,11</t>
+          <t>9,10,11,24,32</t>
         </is>
       </c>
       <c r="F6" t="n">

--- a/tables/datas/common/#Job-职业表.xlsx
+++ b/tables/datas/common/#Job-职业表.xlsx
@@ -481,12 +481,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>(list#sep=,),ESkillId</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>(list#sep=,),ESkillId</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -568,12 +568,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2,3,4,20,21,30</t>
+          <t>烈斩,盾击,旋风斩,战吼,石肤术,挑衅</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2,3,4,20,30</t>
+          <t>烈斩,盾击,旋风斩,战吼,挑衅</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -600,12 +600,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5,6,7,22,23,31</t>
+          <t>火球术,冰霜新星,奥术飞弹,毒雾,冰冻术,燃烧</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5,6,7,22,31</t>
+          <t>火球术,冰霜新星,奥术飞弹,毒雾,燃烧</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -632,12 +632,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9,10,11,24,25,32</t>
+          <t>治疗术,神圣之光,惩击,神圣护盾,祝福,净化</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>9,10,11,24,32</t>
+          <t>治疗术,神圣之光,惩击,神圣护盾,净化</t>
         </is>
       </c>
       <c r="F6" t="n">
